--- a/output/twinmotion/VJH-TM-001_Twinmotion_lists.xlsx
+++ b/output/twinmotion/VJH-TM-001_Twinmotion_lists.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Materials" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Materials!$A$5:$H$49</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Placements!$A$5:$M$93</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Materials!$A$5:$H$48</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Placements!$A$5:$M$78</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="298">
   <si>
     <t xml:space="preserve">Twinmotion lists</t>
   </si>
@@ -35,7 +35,7 @@
     <t xml:space="preserve">CONCEPT DESIGN, NOT FOR CONSTRUCTION</t>
   </si>
   <si>
-    <t xml:space="preserve">Plot 5130272, Saih Shuaib 1, Jebel Ali Hills. Workbook made 2026-10-08 from the export of commit 704ce14 (branch main-pchd8v).</t>
+    <t xml:space="preserve">Plot 5130272, Saih Shuaib 1, Jebel Ali Hills. Workbook made 2026-10-23 from the export of the redesign D-061 (branch main-pchd8v).</t>
   </si>
   <si>
     <t xml:space="preserve">Sheet</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">Back of the piece faces</t>
   </si>
   <si>
-    <t xml:space="preserve">Kitchen run, 1.63 m</t>
+    <t xml:space="preserve">Kitchen run, 3.15 m</t>
   </si>
   <si>
     <t xml:space="preserve">Kitchen base and wall units</t>
@@ -146,16 +146,163 @@
     <t xml:space="preserve">Arabic kitchen</t>
   </si>
   <si>
+    <t xml:space="preserve">W (model -x, toward the road)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dining chair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S (model -y, toward the SSW neighbour)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dining table, 12 seats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dining table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bed, 1.60 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bed, queen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guest bedroom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TV unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TV cabinet with television</t>
+  </si>
+  <si>
     <t xml:space="preserve">E (model +x, toward the landscape plot)</t>
   </si>
   <si>
-    <t xml:space="preserve">Kitchen run, 2.45 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W (model -x, toward the road)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wardrobes, 1.45 m</t>
+    <t xml:space="preserve">Console and mirror</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Console table with mirror</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Washer and dryer, counter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Washing machine and dryer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laundry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N (model +y, toward the NNE neighbour)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coffee table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Living</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sofa, 3.00 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sofa, 3 seats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bed, 0.90 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bed, single</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wardrobe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanity, 1 basin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basin vanity with mirror</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Powder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wall hung WC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Console</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Console table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Island, 2.55 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitchen island</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show kitchen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitchen run, 2.70 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walk in shower with glass screen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toilet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bathtub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freestanding bathtub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanity, 2 basins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Double basin vanity with mirror</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bedroom 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bedroom 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desk and chair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desk with office chair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wardrobes, 1.35 m</t>
   </si>
   <si>
     <t xml:space="preserve">Wardrobe run</t>
@@ -164,207 +311,27 @@
     <t xml:space="preserve">Dress</t>
   </si>
   <si>
-    <t xml:space="preserve">Bed, 1.60 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bed, queen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guest bedroom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N (model +y, toward the NNE neighbour)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desk and chair</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desk with office chair</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TV unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TV cabinet with television</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S (model -y, toward the SSW neighbour)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Washer and dryer, counter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Washing machine and dryer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laundry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coffee table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Living</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sofa, 3.00 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sofa, 3 seats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bed, 0.90 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bed, single</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bookshelves, 1.35 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bookshelf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walk in shower with glass screen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outdoor WC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vanity, 1 basin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basin vanity with mirror</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pantry shelves, 1.74 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shelving unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pantry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pantry shelves, 1.75 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Powder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wall hung WC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Console</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Console table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salon sofa, 2.60 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salon table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coffee table, large</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Island, 3.00 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitchen island</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Show kitchen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toilet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bathtub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freestanding bathtub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vanity, 2 basins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Double basin vanity with mirror</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bedroom 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bedroom 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bedroom 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dressing island</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wardrobes, 3.46 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Family room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armchair</t>
+    <t xml:space="preserve">Wardrobes, 1.92 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wardrobes, 1.93 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wardrobes, 4.80 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Family lounge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bed, 1.93 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bed, king</t>
   </si>
   <si>
     <t xml:space="preserve">Master suite</t>
   </si>
   <si>
-    <t xml:space="preserve">Bed, 1.93 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bed, king</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coffee station, 1.35 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitchenette units</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sitting sofa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sofa, 2 seats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sitting table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coffee table, small</t>
-  </si>
-  <si>
     <t xml:space="preserve">Date palm</t>
   </si>
   <si>
@@ -383,6 +350,12 @@
     <t xml:space="preserve">Tree, Prosopis (ghaf) or acacia</t>
   </si>
   <si>
+    <t xml:space="preserve">olive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tree, Olea europaea (olive), ornamental</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sidr tree</t>
   </si>
   <si>
@@ -431,18 +404,27 @@
     <t xml:space="preserve">Sun elevation (deg)</t>
   </si>
   <si>
-    <t xml:space="preserve">Entrance from the road</t>
+    <t xml:space="preserve">Entrance and carport from the road</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-21 15:00</t>
   </si>
   <si>
-    <t xml:space="preserve">Double height living room</t>
+    <t xml:space="preserve">Double height foyer and the floating stair</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-21 09:00</t>
   </si>
   <si>
+    <t xml:space="preserve">Courtyard from the dining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Family living and the garden glass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master bedroom, the courtyard window</t>
+  </si>
+  <si>
     <t xml:space="preserve">Garden at sunset</t>
   </si>
   <si>
@@ -485,211 +467,196 @@
     <t xml:space="preserve">All palettes</t>
   </si>
   <si>
-    <t xml:space="preserve">Beige render</t>
+    <t xml:space="preserve">Charcoal stone cladding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The entrance stone box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#3B3B3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stone, charcoal or dark basalt, large panels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Twinmotion guide, section 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garden ground</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remaining garden ground</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#C7CCA8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ground, sand or soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggested in this workbook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glazing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All windows and glass doors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#85B2CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glass, clear, low iron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lawn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lawns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#739E4C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grass, short</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lift car and shaft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home elevator car and shaft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#666B73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metal, brushed stainless steel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linear LED line, warm white</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED outlines on the facade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#FFDB99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neon or emissive, warm white 2700 K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partition, painted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interior partition faces without a finish surface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#E6E3DB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paint, as the palette's main wall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paving, light</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paths and the service yard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#CCC7B8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concrete pavers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planting bed, mulch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planting beds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#735C45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ground, bark mulch or soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roof finish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roof terrace floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#DBD9D1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stone pavers or concrete tiles, light grey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slab, rendered edge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slab edges and parapet caps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#F2F2ED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plaster or stucco, as the outside walls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stair, stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stair treads and landings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#D4CCBF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stone, limestone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stone deck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garden terrace, BBQ terrace, entrance court</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#DBCFB5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stone pavers, beige</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#946E4C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wood, teak or iroko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timber, soffits, fins and screens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soffits under the eaves, canopies and the carport; window fins; the BBQ pergola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#9E7045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">White render</t>
   </si>
   <si>
     <t xml:space="preserve">Outside walls, the main render</t>
   </si>
   <si>
-    <t xml:space="preserve">#DBCCB0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plaster or stucco, beige</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Twinmotion guide, section 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garden ground</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remaining garden ground</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#C7CCA8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ground, sand or soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suggested in this workbook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glazing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All windows and glass doors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#85B2CC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glass, clear, low iron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lawn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lawns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#739E4C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grass, short</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lift car and shaft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home elevator car and shaft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#666B73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metal, brushed stainless steel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linear LED line, warm white</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LED outlines on the facade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#FFDB99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neon or emissive, warm white 2700 K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metal, dark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Car gate and pedestrian gate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#333333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metal, dark grey powder coat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partition, painted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interior partition faces without a finish surface</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#E6E3DB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paint, as the palette's main wall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paving, light</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paths and the service yard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#CCC7B8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concrete pavers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planting bed, mulch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planting beds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#735C45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ground, bark mulch or soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roof finish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roof terrace floor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#DBD9D1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stone pavers or concrete tiles, light grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slab, rendered edge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slab edges and parapet caps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#EDEBE3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plaster or stucco, as the outside walls</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stair, stone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stair treads and landings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#D4CCBF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stone, limestone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stone deck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garden terrace, BBQ terrace, entrance court</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#DBCFB5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stone pavers, beige</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Timber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#946E4C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wood, teak or iroko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Timber, soffits, fins and pergola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soffits, fins, roof and BBQ pergolas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#99633B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warm split face stone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entrance portal and the garden frame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#C7AD80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stone, split face or rock face, warm</t>
+    <t xml:space="preserve">Plaster or stucco, white, smooth</t>
   </si>
   <si>
     <t xml:space="preserve">1, Sand and Oak</t>
@@ -1041,7 +1008,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="46">
+  <fills count="44">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1051,19 +1018,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF3A3F47"/>
-        <bgColor rgb="FF4A4947"/>
+        <bgColor rgb="FF3B3B3D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF3F1EC"/>
-        <bgColor rgb="FFF4F2EE"/>
+        <bgColor rgb="FFF2F2ED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDBCCB0"/>
-        <bgColor rgb="FFD9CCB4"/>
+        <fgColor rgb="FF3B3B3D"/>
+        <bgColor rgb="FF3A3F47"/>
       </patternFill>
     </fill>
     <fill>
@@ -1098,12 +1065,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF333333"/>
-        <bgColor rgb="FF3A3F47"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE6E3DB"/>
         <bgColor rgb="FFEAE6DF"/>
       </patternFill>
@@ -1128,8 +1089,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEDEBE3"/>
-        <bgColor rgb="FFEEEBE6"/>
+        <fgColor rgb="FFF2F2ED"/>
+        <bgColor rgb="FFF3F1EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -1147,31 +1108,25 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF946E4C"/>
-        <bgColor rgb="FF99633B"/>
+        <bgColor rgb="FF9E7045"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99633B"/>
+        <fgColor rgb="FF9E7045"/>
         <bgColor rgb="FF946E4C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC7AD80"/>
-        <bgColor rgb="FFC9A77C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC9A77C"/>
-        <bgColor rgb="FFC7AD80"/>
+        <bgColor rgb="FFA9A7A2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9CCB4"/>
-        <bgColor rgb="FFDBCCB0"/>
+        <bgColor rgb="FFDBCFB5"/>
       </patternFill>
     </fill>
     <fill>
@@ -1225,7 +1180,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEEBE6"/>
-        <bgColor rgb="FFEDEBE3"/>
+        <bgColor rgb="FFF0EDE8"/>
       </patternFill>
     </fill>
     <fill>
@@ -1243,7 +1198,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F2EE"/>
-        <bgColor rgb="FFF3F1EC"/>
+        <bgColor rgb="FFF2F2ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -1285,7 +1240,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA9A7A2"/>
-        <bgColor rgb="FFC7AD80"/>
+        <bgColor rgb="FFC9A77C"/>
       </patternFill>
     </fill>
     <fill>
@@ -1362,7 +1317,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="58">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1595,14 +1550,6 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="44" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="45" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1612,7 +1559,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="46">
+  <dxfs count="44">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1647,7 +1594,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF333333"/>
+          <fgColor rgb="FF3B3B3D"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1719,7 +1666,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF99633B"/>
+          <fgColor rgb="FF9E7045"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1736,14 +1683,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFC4C2BD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC7AD80"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1855,14 +1794,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFDBCCB0"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFDBCFB5"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -1911,14 +1842,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFEDEBE3"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFEEEBE6"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -1936,6 +1859,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF2ECE1"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF2F2ED"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1985,60 +1916,60 @@
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFAFAF9"/>
-      <rgbColor rgb="FFE0D4BF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFE6E3DB"/>
       <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFDBCCB0"/>
-      <rgbColor rgb="FFEBE7E1"/>
+      <rgbColor rgb="FFDBCFB5"/>
+      <rgbColor rgb="FFF3F1EC"/>
       <rgbColor rgb="FFD9D6D0"/>
       <rgbColor rgb="FFB00000"/>
-      <rgbColor rgb="FFEAE6DF"/>
+      <rgbColor rgb="FFF0EDE8"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF946E4C"/>
-      <rgbColor rgb="FFF0EDE8"/>
-      <rgbColor rgb="FFD6CFC2"/>
+      <rgbColor rgb="FF9E7045"/>
+      <rgbColor rgb="FFFAFAF9"/>
+      <rgbColor rgb="FFD9D2C6"/>
       <rgbColor rgb="FFC4C2BD"/>
       <rgbColor rgb="FF8A7663"/>
       <rgbColor rgb="FF85B2CC"/>
       <rgbColor rgb="FF7A5236"/>
       <rgbColor rgb="FFF6F2EA"/>
-      <rgbColor rgb="FFF7F7F5"/>
+      <rgbColor rgb="FFF2F2ED"/>
       <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFC7AD80"/>
-      <rgbColor rgb="FFE6E3DB"/>
+      <rgbColor rgb="FFD8C3A0"/>
+      <rgbColor rgb="FFEBE7E1"/>
       <rgbColor rgb="FFD3D1CC"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFEEEBE6"/>
-      <rgbColor rgb="FFDBCFB5"/>
+      <rgbColor rgb="FFF4F2EE"/>
+      <rgbColor rgb="FFE0D4BF"/>
       <rgbColor rgb="FFDBD9D1"/>
-      <rgbColor rgb="FFF3F1EC"/>
+      <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FFD9D2C6"/>
+      <rgbColor rgb="FFEAE6DF"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFCFCDC8"/>
-      <rgbColor rgb="FFF4F2EE"/>
-      <rgbColor rgb="FFEDEBE3"/>
+      <rgbColor rgb="FFF7F7F5"/>
+      <rgbColor rgb="FFEEEBE6"/>
       <rgbColor rgb="FFF2ECE1"/>
       <rgbColor rgb="FFC9C7C2"/>
       <rgbColor rgb="FFC9A77C"/>
       <rgbColor rgb="FFC8C4BC"/>
       <rgbColor rgb="FFFFDB99"/>
-      <rgbColor rgb="FFD4CCBF"/>
+      <rgbColor rgb="FFD6CFC2"/>
       <rgbColor rgb="FFCCC7B8"/>
       <rgbColor rgb="FFC7CCA8"/>
-      <rgbColor rgb="FFD8C3A0"/>
       <rgbColor rgb="FFCFC1A6"/>
       <rgbColor rgb="FFD9CCB4"/>
+      <rgbColor rgb="FFD4CCBF"/>
       <rgbColor rgb="FF666B73"/>
       <rgbColor rgb="FFA9A7A2"/>
       <rgbColor rgb="FF555555"/>
       <rgbColor rgb="FF739E4C"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF3A3F47"/>
-      <rgbColor rgb="FF99633B"/>
+      <rgbColor rgb="FF946E4C"/>
       <rgbColor rgb="FF735C45"/>
       <rgbColor rgb="FF4A4947"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="FF3B3B3D"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -2271,8 +2202,8 @@
         <v>6</v>
       </c>
       <c r="B6" s="5" t="n">
-        <f aca="false">COUNTA(Placements!B6:B93)</f>
-        <v>88</v>
+        <f aca="false">COUNTA(Placements!B6:B78)</f>
+        <v>73</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>7</v>
@@ -2283,8 +2214,8 @@
         <v>8</v>
       </c>
       <c r="B7" s="5" t="n">
-        <f aca="false">COUNTA(Cameras!B6:B11)</f>
-        <v>6</v>
+        <f aca="false">COUNTA(Cameras!B6:B12)</f>
+        <v>7</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>9</v>
@@ -2295,8 +2226,8 @@
         <v>10</v>
       </c>
       <c r="B8" s="5" t="n">
-        <f aca="false">COUNTA(Materials!C6:C49)</f>
-        <v>44</v>
+        <f aca="false">COUNTA(Materials!C6:C48)</f>
+        <v>43</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>11</v>
@@ -2312,8 +2243,8 @@
         <v>13</v>
       </c>
       <c r="B11" s="7" t="n">
-        <f aca="false">COUNTIF(Placements!E6:E93,A11)</f>
-        <v>36</v>
+        <f aca="false">COUNTIF(Placements!E6:E78,A11)</f>
+        <v>33</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2321,8 +2252,8 @@
         <v>14</v>
       </c>
       <c r="B12" s="7" t="n">
-        <f aca="false">COUNTIF(Placements!E6:E93,A12)</f>
-        <v>38</v>
+        <f aca="false">COUNTIF(Placements!E6:E78,A12)</f>
+        <v>23</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2330,8 +2261,8 @@
         <v>15</v>
       </c>
       <c r="B13" s="7" t="n">
-        <f aca="false">COUNTIF(Placements!E6:E93,A13)</f>
-        <v>14</v>
+        <f aca="false">COUNTIF(Placements!E6:E78,A13)</f>
+        <v>17</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2340,7 +2271,7 @@
       </c>
       <c r="B14" s="8" t="n">
         <f aca="false">SUM(B11:B13)</f>
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2393,7 +2324,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M95"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -2481,16 +2412,16 @@
         <v>13</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>20.73</v>
+        <v>11.21</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>9.05</v>
+        <v>13.4</v>
       </c>
       <c r="H6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>1.63</v>
+        <v>3.15</v>
       </c>
       <c r="J6" s="12" t="n">
         <v>0.62</v>
@@ -2499,7 +2430,7 @@
         <v>2.25</v>
       </c>
       <c r="L6" s="13" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="M6" s="11" t="s">
         <v>39</v>
@@ -2513,37 +2444,37 @@
         <v>40</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>18.96</v>
+        <v>15.39</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>7.57</v>
+        <v>20.48</v>
       </c>
       <c r="H7" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>2.45</v>
+        <v>0.48</v>
       </c>
       <c r="J7" s="14" t="n">
-        <v>0.62</v>
+        <v>0.46</v>
       </c>
       <c r="K7" s="14" t="n">
-        <v>2.25</v>
+        <v>0.92</v>
       </c>
       <c r="L7" s="15" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2551,40 +2482,40 @@
         <v>3</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>9.24</v>
+        <v>17.16</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>28.46</v>
+        <v>20.48</v>
       </c>
       <c r="H8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>1.45</v>
+        <v>0.48</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="K8" s="12" t="n">
-        <v>2.4</v>
+        <v>0.92</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2592,40 +2523,40 @@
         <v>4</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>5.59</v>
+        <v>15.39</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>25.62</v>
+        <v>19.88</v>
       </c>
       <c r="H9" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>2.7</v>
+        <v>0.48</v>
       </c>
       <c r="J9" s="14" t="n">
-        <v>2.18</v>
+        <v>0.46</v>
       </c>
       <c r="K9" s="14" t="n">
-        <v>1.25</v>
+        <v>0.92</v>
       </c>
       <c r="L9" s="15" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2633,40 +2564,40 @@
         <v>5</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>4.61</v>
+        <v>17.16</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>23.57</v>
+        <v>19.88</v>
       </c>
       <c r="H10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>1.2</v>
+        <v>0.48</v>
       </c>
       <c r="J10" s="12" t="n">
-        <v>1.13</v>
+        <v>0.46</v>
       </c>
       <c r="K10" s="12" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2674,40 +2605,40 @@
         <v>6</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>4.99</v>
+        <v>15.39</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>22.45</v>
+        <v>19.27</v>
       </c>
       <c r="H11" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>1.8</v>
+        <v>0.48</v>
       </c>
       <c r="J11" s="14" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="K11" s="14" t="n">
-        <v>2</v>
+        <v>0.92</v>
       </c>
       <c r="L11" s="15" t="n">
         <v>0</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2715,40 +2646,40 @@
         <v>7</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>18.23</v>
+        <v>17.16</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>7.52</v>
+        <v>19.27</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>1.4</v>
+        <v>0.48</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>0.62</v>
+        <v>0.46</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2756,40 +2687,40 @@
         <v>8</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>18.04</v>
+        <v>15.39</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>21.42</v>
+        <v>18.68</v>
       </c>
       <c r="H13" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>1.3</v>
+        <v>0.48</v>
       </c>
       <c r="J13" s="14" t="n">
-        <v>0.7</v>
+        <v>0.46</v>
       </c>
       <c r="K13" s="14" t="n">
-        <v>0.4</v>
+        <v>0.92</v>
       </c>
       <c r="L13" s="15" t="n">
         <v>0</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2797,40 +2728,40 @@
         <v>9</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>18.04</v>
+        <v>17.16</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>21.07</v>
+        <v>18.68</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>3</v>
+        <v>0.48</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>2.2</v>
+        <v>0.46</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>0.01</v>
+        <v>0.92</v>
       </c>
       <c r="L14" s="13" t="n">
         <v>0</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2838,40 +2769,40 @@
         <v>10</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>18.04</v>
+        <v>15.39</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>20.44</v>
+        <v>18.07</v>
       </c>
       <c r="H15" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>3</v>
+        <v>0.48</v>
       </c>
       <c r="J15" s="14" t="n">
-        <v>0.95</v>
+        <v>0.46</v>
       </c>
       <c r="K15" s="14" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="L15" s="15" t="n">
         <v>0</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2879,40 +2810,40 @@
         <v>11</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>18.54</v>
+        <v>17.16</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>23.69</v>
+        <v>18.07</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>2.4</v>
+        <v>0.48</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>2</v>
+        <v>0.92</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2920,40 +2851,40 @@
         <v>12</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>14.38</v>
+        <v>16.27</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>8.72</v>
+        <v>19.27</v>
       </c>
       <c r="H17" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="J17" s="14" t="n">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="K17" s="14" t="n">
-        <v>1.25</v>
+        <v>0.74</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2961,40 +2892,40 @@
         <v>13</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>6.54</v>
+        <v>10.24</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>14.51</v>
+        <v>28.05</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>1.35</v>
+        <v>2.7</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>0.38</v>
+        <v>2.18</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3002,22 +2933,22 @@
         <v>14</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>50</v>
-      </c>
       <c r="D19" s="5" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>7.69</v>
+        <v>13.43</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>17.49</v>
+        <v>27.95</v>
       </c>
       <c r="H19" s="14" t="n">
         <v>0</v>
@@ -3026,16 +2957,16 @@
         <v>1.8</v>
       </c>
       <c r="J19" s="14" t="n">
-        <v>1.45</v>
+        <v>0.45</v>
       </c>
       <c r="K19" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3043,40 +2974,40 @@
         <v>15</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>10.59</v>
+        <v>6.62</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>9.67</v>
+        <v>15.45</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="L20" s="13" t="n">
         <v>0</v>
       </c>
       <c r="M20" s="11" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3084,40 +3015,40 @@
         <v>16</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>10.59</v>
+        <v>9.7</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>10.44</v>
+        <v>14.69</v>
       </c>
       <c r="H21" s="14" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J21" s="14" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="K21" s="14" t="n">
-        <v>1.7</v>
+        <v>0.89</v>
       </c>
       <c r="L21" s="15" t="n">
         <v>180</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3125,40 +3056,40 @@
         <v>17</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>15.27</v>
+        <v>16.3</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>11.17</v>
+        <v>26.8</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>1.74</v>
+        <v>0.7</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>0.45</v>
+        <v>1.3</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3166,40 +3097,40 @@
         <v>18</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>15.94</v>
+        <v>16.65</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>10.05</v>
+        <v>26.8</v>
       </c>
       <c r="H23" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="J23" s="14" t="n">
-        <v>0.45</v>
+        <v>3</v>
       </c>
       <c r="K23" s="14" t="n">
-        <v>2.2</v>
+        <v>0.01</v>
       </c>
       <c r="L23" s="15" t="n">
         <v>0</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3207,40 +3138,40 @@
         <v>19</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>15.94</v>
+        <v>17.27</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>12.29</v>
+        <v>26.8</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>1.75</v>
+        <v>0.95</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>0.45</v>
+        <v>3</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>2.2</v>
+        <v>0.85</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3248,40 +3179,40 @@
         <v>20</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>14.09</v>
+        <v>14.03</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>10.09</v>
+        <v>26.8</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J25" s="14" t="n">
-        <v>0.55</v>
+        <v>0.45</v>
       </c>
       <c r="K25" s="14" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="L25" s="15" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3289,40 +3220,40 @@
         <v>21</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>14.09</v>
+        <v>5.45</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>11.81</v>
+        <v>13.96</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>0.62</v>
+        <v>2.08</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L26" s="13" t="n">
         <v>180</v>
       </c>
       <c r="M26" s="11" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3330,40 +3261,40 @@
         <v>22</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>10</v>
+        <v>4.55</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>26.95</v>
+        <v>14.4</v>
       </c>
       <c r="H27" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J27" s="14" t="n">
-        <v>0.42</v>
+        <v>0.6</v>
       </c>
       <c r="K27" s="14" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="L27" s="15" t="n">
         <v>-90</v>
       </c>
       <c r="M27" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3371,40 +3302,40 @@
         <v>23</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>13.54</v>
+        <v>8.28</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>27.12</v>
+        <v>23.73</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>3.1</v>
+        <v>0.55</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>0.01</v>
+        <v>1.7</v>
       </c>
       <c r="L28" s="13" t="n">
         <v>0</v>
       </c>
       <c r="M28" s="11" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3412,40 +3343,40 @@
         <v>24</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>13.54</v>
+        <v>8.28</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>25.45</v>
+        <v>25.29</v>
       </c>
       <c r="H29" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J29" s="14" t="n">
-        <v>0.95</v>
+        <v>0.62</v>
       </c>
       <c r="K29" s="14" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="L29" s="15" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3453,40 +3384,40 @@
         <v>25</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>13.54</v>
+        <v>8.79</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>28.8</v>
+        <v>27.95</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>0.95</v>
+        <v>0.42</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L30" s="13" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M30" s="11" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3494,40 +3425,40 @@
         <v>26</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>13.54</v>
+        <v>16.27</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>27.12</v>
+        <v>12.57</v>
       </c>
       <c r="H31" s="14" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>1.6</v>
+        <v>2.55</v>
       </c>
       <c r="J31" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" s="14" t="n">
         <v>0.9</v>
       </c>
-      <c r="K31" s="14" t="n">
-        <v>0.4</v>
-      </c>
       <c r="L31" s="15" t="n">
         <v>0</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3535,40 +3466,40 @@
         <v>27</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>18.04</v>
+        <v>14.11</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>14.77</v>
+        <v>11.53</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>0.9</v>
+        <v>2.25</v>
       </c>
       <c r="L32" s="13" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="M32" s="11" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3576,22 +3507,22 @@
         <v>28</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>5.54</v>
+        <v>11.25</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>27.27</v>
+        <v>24.52</v>
       </c>
       <c r="H33" s="14" t="n">
         <v>0</v>
@@ -3606,10 +3537,10 @@
         <v>2</v>
       </c>
       <c r="L33" s="15" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3617,22 +3548,22 @@
         <v>29</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>4.64</v>
+        <v>12.22</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>27.1</v>
+        <v>23.73</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>0.3</v>
@@ -3650,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="11" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3658,22 +3589,22 @@
         <v>30</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>6.34</v>
+        <v>12.93</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>27.13</v>
+        <v>23.76</v>
       </c>
       <c r="H35" s="14" t="n">
         <v>0</v>
@@ -3691,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="M35" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3699,22 +3630,22 @@
         <v>31</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>12.49</v>
+        <v>7.75</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>6.77</v>
+        <v>12.25</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>0</v>
@@ -3732,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="M36" s="11" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3740,40 +3671,40 @@
         <v>32</v>
       </c>
       <c r="B37" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>69</v>
-      </c>
       <c r="D37" s="5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>7.69</v>
+        <v>7.75</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>12.77</v>
+        <v>14.72</v>
       </c>
       <c r="H37" s="14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J37" s="14" t="n">
-        <v>0.9</v>
+        <v>0.55</v>
       </c>
       <c r="K37" s="14" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="L37" s="15" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3781,40 +3712,40 @@
         <v>33</v>
       </c>
       <c r="B38" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C38" s="11" t="s">
-        <v>72</v>
-      </c>
       <c r="D38" s="11" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>12.49</v>
+        <v>7.31</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>8.84</v>
+        <v>14.1</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="M38" s="11" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3822,40 +3753,40 @@
         <v>34</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>6.79</v>
+        <v>17.55</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>12.6</v>
+        <v>14.6</v>
       </c>
       <c r="H39" s="14" t="n">
-        <v>0.3</v>
+        <v>5</v>
       </c>
       <c r="I39" s="14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J39" s="14" t="n">
         <v>0.8</v>
       </c>
-      <c r="J39" s="14" t="n">
-        <v>0.55</v>
-      </c>
       <c r="K39" s="14" t="n">
-        <v>1.7</v>
+        <v>0.58</v>
       </c>
       <c r="L39" s="15" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M39" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3863,40 +3794,40 @@
         <v>35</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>8.49</v>
+        <v>17.55</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>12.63</v>
+        <v>10.6</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>0.62</v>
+        <v>0.9</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" s="13" t="n">
         <v>0</v>
       </c>
       <c r="M40" s="11" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3904,40 +3835,40 @@
         <v>36</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>12.49</v>
+        <v>10.32</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>9.5</v>
+        <v>23.9</v>
       </c>
       <c r="H41" s="14" t="n">
-        <v>0.3</v>
+        <v>5</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J41" s="14" t="n">
-        <v>0.55</v>
+        <v>0.9</v>
       </c>
       <c r="K41" s="14" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="L41" s="15" t="n">
         <v>0</v>
       </c>
       <c r="M41" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3945,40 +3876,40 @@
         <v>37</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E42" s="11" t="s">
         <v>14</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>8.34</v>
+        <v>17.55</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>9.91</v>
+        <v>23.9</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>0.58</v>
+        <v>2</v>
       </c>
       <c r="L42" s="13" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M42" s="11" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3986,40 +3917,40 @@
         <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>69</v>
-      </c>
       <c r="D43" s="5" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>8.34</v>
+        <v>9.43</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>6.76</v>
+        <v>24.52</v>
       </c>
       <c r="H43" s="14" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J43" s="14" t="n">
-        <v>0.9</v>
+        <v>0.55</v>
       </c>
       <c r="K43" s="14" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="L43" s="15" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="M43" s="5" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4027,40 +3958,40 @@
         <v>39</v>
       </c>
       <c r="B44" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C44" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="11" t="s">
-        <v>69</v>
-      </c>
       <c r="D44" s="11" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E44" s="11" t="s">
         <v>14</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>7.49</v>
+        <v>16.62</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>10.87</v>
+        <v>24.52</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>0.9</v>
+        <v>0.55</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="L44" s="13" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="M44" s="11" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4068,40 +3999,40 @@
         <v>40</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>5.54</v>
+        <v>16.62</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>27.27</v>
+        <v>11.23</v>
       </c>
       <c r="H45" s="14" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J45" s="14" t="n">
-        <v>0.9</v>
+        <v>0.55</v>
       </c>
       <c r="K45" s="14" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="L45" s="15" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="M45" s="5" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4109,40 +4040,40 @@
         <v>41</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E46" s="11" t="s">
         <v>14</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>19.05</v>
+        <v>16.66</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>28.98</v>
+        <v>13.28</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>0.9</v>
+        <v>0.62</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L46" s="13" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="M46" s="11" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4150,40 +4081,40 @@
         <v>42</v>
       </c>
       <c r="B47" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>72</v>
-      </c>
       <c r="D47" s="5" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>6.59</v>
+        <v>11.12</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>10.69</v>
+        <v>23.76</v>
       </c>
       <c r="H47" s="14" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J47" s="14" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="K47" s="14" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="L47" s="15" t="n">
         <v>0</v>
       </c>
       <c r="M47" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4191,40 +4122,40 @@
         <v>43</v>
       </c>
       <c r="B48" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C48" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C48" s="11" t="s">
-        <v>72</v>
-      </c>
       <c r="D48" s="11" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E48" s="11" t="s">
         <v>14</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>4.64</v>
+        <v>18.35</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>27.1</v>
+        <v>23.76</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="L48" s="13" t="n">
         <v>0</v>
       </c>
       <c r="M48" s="11" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4232,40 +4163,40 @@
         <v>44</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>19.95</v>
+        <v>10.24</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>28.8</v>
+        <v>27.95</v>
       </c>
       <c r="H49" s="14" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>0.55</v>
+        <v>2.18</v>
       </c>
       <c r="K49" s="14" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="L49" s="15" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="M49" s="5" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4273,40 +4204,40 @@
         <v>45</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E50" s="11" t="s">
         <v>14</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>10.07</v>
+        <v>13.43</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>7.41</v>
+        <v>27.95</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>0.55</v>
+        <v>0.45</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="L50" s="13" t="n">
         <v>90</v>
       </c>
       <c r="M50" s="11" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4314,40 +4245,40 @@
         <v>46</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F51" s="14" t="n">
-        <v>7.34</v>
+        <v>14.89</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>6.62</v>
+        <v>27.95</v>
       </c>
       <c r="H51" s="14" t="n">
         <v>5</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J51" s="14" t="n">
-        <v>0.62</v>
+        <v>2.18</v>
       </c>
       <c r="K51" s="14" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L51" s="15" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="M51" s="5" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4355,40 +4286,40 @@
         <v>47</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E52" s="11" t="s">
         <v>14</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>8.29</v>
+        <v>16.27</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>10.73</v>
+        <v>26.31</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>0.62</v>
+        <v>1.13</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L52" s="13" t="n">
         <v>0</v>
       </c>
       <c r="M52" s="11" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4396,10 +4327,10 @@
         <v>48</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>93</v>
@@ -4408,28 +4339,28 @@
         <v>14</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>6.34</v>
+        <v>15.4</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>27.13</v>
+        <v>23.75</v>
       </c>
       <c r="H53" s="14" t="n">
         <v>5</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>0.5</v>
+        <v>1.35</v>
       </c>
       <c r="J53" s="14" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="K53" s="14" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="L53" s="15" t="n">
         <v>0</v>
       </c>
       <c r="M53" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4437,10 +4368,10 @@
         <v>49</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D54" s="11" t="s">
         <v>93</v>
@@ -4449,28 +4380,28 @@
         <v>14</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>19.85</v>
+        <v>15.9</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>30</v>
+        <v>11.14</v>
       </c>
       <c r="H54" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>0.5</v>
+        <v>1.92</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="L54" s="13" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M54" s="11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4478,40 +4409,40 @@
         <v>50</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E55" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>7.1</v>
+        <v>15.9</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>13.91</v>
+        <v>14.01</v>
       </c>
       <c r="H55" s="14" t="n">
         <v>5</v>
       </c>
       <c r="I55" s="14" t="n">
-        <v>2.7</v>
+        <v>1.93</v>
       </c>
       <c r="J55" s="14" t="n">
-        <v>2.18</v>
+        <v>0.6</v>
       </c>
       <c r="K55" s="14" t="n">
-        <v>1.25</v>
+        <v>2.4</v>
       </c>
       <c r="L55" s="15" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M55" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4519,40 +4450,40 @@
         <v>51</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E56" s="11" t="s">
         <v>14</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>5.61</v>
+        <v>14.1</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>15.57</v>
+        <v>12.57</v>
       </c>
       <c r="H56" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>1.13</v>
+        <v>0.6</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="L56" s="13" t="n">
         <v>-90</v>
       </c>
       <c r="M56" s="11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4560,40 +4491,40 @@
         <v>52</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E57" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F57" s="14" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>18.09</v>
+        <v>27.95</v>
       </c>
       <c r="H57" s="14" t="n">
         <v>5</v>
       </c>
       <c r="I57" s="14" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J57" s="14" t="n">
-        <v>0.45</v>
+        <v>1.3</v>
       </c>
       <c r="K57" s="14" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="L57" s="15" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M57" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4601,10 +4532,10 @@
         <v>53</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D58" s="11" t="s">
         <v>97</v>
@@ -4613,28 +4544,28 @@
         <v>14</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>6.79</v>
+        <v>6.15</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>23.31</v>
+        <v>27.95</v>
       </c>
       <c r="H58" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>2.18</v>
+        <v>3</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>1.25</v>
+        <v>0.01</v>
       </c>
       <c r="L58" s="13" t="n">
         <v>0</v>
       </c>
       <c r="M58" s="11" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4642,10 +4573,10 @@
         <v>54</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>97</v>
@@ -4654,28 +4585,28 @@
         <v>14</v>
       </c>
       <c r="F59" s="14" t="n">
-        <v>4.61</v>
+        <v>5.53</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>24.47</v>
+        <v>27.95</v>
       </c>
       <c r="H59" s="14" t="n">
         <v>5</v>
       </c>
       <c r="I59" s="14" t="n">
-        <v>1.2</v>
+        <v>0.95</v>
       </c>
       <c r="J59" s="14" t="n">
-        <v>1.13</v>
+        <v>3</v>
       </c>
       <c r="K59" s="14" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L59" s="15" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="M59" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4683,10 +4614,10 @@
         <v>55</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D60" s="11" t="s">
         <v>97</v>
@@ -4695,16 +4626,16 @@
         <v>14</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>6.19</v>
+        <v>8.78</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>26.49</v>
+        <v>27.95</v>
       </c>
       <c r="H60" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J60" s="12" t="n">
         <v>0.45</v>
@@ -4713,10 +4644,10 @@
         <v>2</v>
       </c>
       <c r="L60" s="13" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M60" s="11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4724,28 +4655,28 @@
         <v>56</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E61" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F61" s="14" t="n">
-        <v>18.37</v>
+        <v>14.89</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>25.16</v>
+        <v>17.55</v>
       </c>
       <c r="H61" s="14" t="n">
         <v>5</v>
       </c>
       <c r="I61" s="14" t="n">
-        <v>2.7</v>
+        <v>3.03</v>
       </c>
       <c r="J61" s="14" t="n">
         <v>2.18</v>
@@ -4754,10 +4685,10 @@
         <v>1.25</v>
       </c>
       <c r="L61" s="15" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="M61" s="5" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4765,1292 +4696,671 @@
         <v>57</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>98</v>
+        <v>15</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>15.61</v>
+        <v>29.3</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>26.24</v>
+        <v>6</v>
       </c>
       <c r="H62" s="12" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="I62" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I62" s="12" t="n">
-        <v>1.2</v>
-      </c>
       <c r="J62" s="12" t="n">
-        <v>1.13</v>
+        <v>5</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>0.9</v>
+        <v>7</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>-90</v>
-      </c>
-      <c r="M62" s="11" t="s">
-        <v>41</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M62" s="11"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="n">
         <v>58</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>98</v>
+        <v>15</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F63" s="14" t="n">
-        <v>18.4</v>
+        <v>29.3</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>28.19</v>
+        <v>12.5</v>
       </c>
       <c r="H63" s="14" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="I63" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="I63" s="14" t="n">
-        <v>1.8</v>
-      </c>
       <c r="J63" s="14" t="n">
-        <v>0.45</v>
+        <v>5</v>
       </c>
       <c r="K63" s="14" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L63" s="15" t="n">
-        <v>180</v>
-      </c>
-      <c r="M63" s="5" t="s">
-        <v>48</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M63" s="5"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="11" t="n">
         <v>59</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>12.69</v>
+        <v>29.3</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>8.31</v>
+        <v>23.5</v>
       </c>
       <c r="H64" s="12" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="I64" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I64" s="12" t="n">
-        <v>1.6</v>
-      </c>
       <c r="J64" s="12" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>0.93</v>
+        <v>7</v>
       </c>
       <c r="L64" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="M64" s="11" t="s">
-        <v>53</v>
-      </c>
+      <c r="M64" s="11"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="n">
         <v>60</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F65" s="14" t="n">
-        <v>9.24</v>
+        <v>1.5</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>28.47</v>
+        <v>32.8</v>
       </c>
       <c r="H65" s="14" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="I65" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="I65" s="14" t="n">
-        <v>1.45</v>
-      </c>
       <c r="J65" s="14" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="K65" s="14" t="n">
-        <v>2.4</v>
+        <v>7</v>
       </c>
       <c r="L65" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="M65" s="5" t="s">
-        <v>39</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M65" s="5"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="11" t="n">
         <v>61</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>12.19</v>
+        <v>7</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>6.61</v>
+        <v>33.3</v>
       </c>
       <c r="H66" s="12" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="I66" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I66" s="12" t="n">
-        <v>3.46</v>
-      </c>
       <c r="J66" s="12" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>2.4</v>
+        <v>7</v>
       </c>
       <c r="L66" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="M66" s="11" t="s">
-        <v>53</v>
-      </c>
+      <c r="M66" s="11"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="n">
         <v>62</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F67" s="14" t="n">
-        <v>12.19</v>
+        <v>1.5</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>10.01</v>
+        <v>1.6</v>
       </c>
       <c r="H67" s="14" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="I67" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="I67" s="14" t="n">
-        <v>3.46</v>
-      </c>
       <c r="J67" s="14" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="K67" s="14" t="n">
-        <v>2.4</v>
+        <v>7</v>
       </c>
       <c r="L67" s="15" t="n">
-        <v>180</v>
-      </c>
-      <c r="M67" s="5" t="s">
-        <v>48</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M67" s="5"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="11" t="n">
         <v>63</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>12.3</v>
+        <v>25</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>26.6</v>
+        <v>1.6</v>
       </c>
       <c r="H68" s="12" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="I68" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I68" s="12" t="n">
-        <v>0.7</v>
-      </c>
       <c r="J68" s="12" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>0.4</v>
+        <v>7</v>
       </c>
       <c r="L68" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="M68" s="11" t="s">
-        <v>53</v>
-      </c>
+      <c r="M68" s="11"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="n">
         <v>64</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F69" s="14" t="n">
-        <v>12.65</v>
+        <v>25</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>26.6</v>
+        <v>32.6</v>
       </c>
       <c r="H69" s="14" t="n">
-        <v>5</v>
+        <v>-0.45</v>
       </c>
       <c r="I69" s="14" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="J69" s="14" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K69" s="14" t="n">
-        <v>0.01</v>
+        <v>4</v>
       </c>
       <c r="L69" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="M69" s="5" t="s">
-        <v>53</v>
-      </c>
+      <c r="M69" s="5"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="11" t="n">
         <v>65</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>13.27</v>
+        <v>16</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>26.6</v>
+        <v>32.6</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>5</v>
+        <v>-0.45</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>0.95</v>
+        <v>3.5</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>0.85</v>
+        <v>4</v>
       </c>
       <c r="L70" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="M70" s="11" t="s">
-        <v>53</v>
-      </c>
+      <c r="M70" s="11"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="n">
         <v>66</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F71" s="14" t="n">
-        <v>10.02</v>
+        <v>25</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>26.6</v>
+        <v>15.5</v>
       </c>
       <c r="H71" s="14" t="n">
-        <v>5</v>
+        <v>-0.45</v>
       </c>
       <c r="I71" s="14" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J71" s="14" t="n">
-        <v>0.45</v>
+        <v>3.5</v>
       </c>
       <c r="K71" s="14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L71" s="15" t="n">
-        <v>-90</v>
-      </c>
-      <c r="M71" s="5" t="s">
-        <v>41</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M71" s="5"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="11" t="n">
         <v>67</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>17</v>
+        <v>1.8</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>8.84</v>
+        <v>11.5</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>5</v>
+        <v>-0.45</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>0.85</v>
+        <v>3.5</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>0.85</v>
+        <v>3.5</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="L72" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="M72" s="11" t="s">
-        <v>53</v>
-      </c>
+      <c r="M72" s="11"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="n">
         <v>68</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F73" s="14" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>8.84</v>
+        <v>14.2</v>
       </c>
       <c r="H73" s="14" t="n">
-        <v>5</v>
+        <v>-0.45</v>
       </c>
       <c r="I73" s="14" t="n">
-        <v>0.85</v>
+        <v>3.5</v>
       </c>
       <c r="J73" s="14" t="n">
-        <v>0.85</v>
+        <v>3.5</v>
       </c>
       <c r="K73" s="14" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="L73" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="M73" s="5" t="s">
-        <v>53</v>
-      </c>
+      <c r="M73" s="5"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="11" t="n">
         <v>69</v>
       </c>
       <c r="B74" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C74" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C74" s="11" t="s">
-        <v>105</v>
-      </c>
       <c r="D74" s="11" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>18.38</v>
+        <v>1.8</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>12.72</v>
+        <v>20.5</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>5</v>
+        <v>-0.45</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>3.03</v>
+        <v>3.5</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>2.18</v>
+        <v>3.5</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="L74" s="13" t="n">
-        <v>180</v>
-      </c>
-      <c r="M74" s="11" t="s">
-        <v>48</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M74" s="11"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="n">
         <v>70</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>15.35</v>
+        <v>1.8</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>12.06</v>
+        <v>27.5</v>
       </c>
       <c r="H75" s="14" t="n">
-        <v>5</v>
+        <v>-0.45</v>
       </c>
       <c r="I75" s="14" t="n">
-        <v>1.35</v>
+        <v>3.5</v>
       </c>
       <c r="J75" s="14" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="K75" s="14" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="L75" s="15" t="n">
-        <v>-90</v>
-      </c>
-      <c r="M75" s="5" t="s">
-        <v>41</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M75" s="5"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="11" t="n">
         <v>71</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>15.61</v>
+        <v>29.1</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>10.86</v>
+        <v>18.5</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>5</v>
+        <v>-0.45</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>1.13</v>
+        <v>6</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>0.9</v>
+        <v>7</v>
       </c>
       <c r="L76" s="13" t="n">
-        <v>-90</v>
-      </c>
-      <c r="M76" s="11" t="s">
-        <v>41</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M76" s="11"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="n">
         <v>72</v>
       </c>
       <c r="B77" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C77" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C77" s="5" t="s">
-        <v>109</v>
-      </c>
       <c r="D77" s="5" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F77" s="14" t="n">
-        <v>17.6</v>
+        <v>11.4</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>6.79</v>
+        <v>17.55</v>
       </c>
       <c r="H77" s="14" t="n">
-        <v>5</v>
+        <v>-0.45</v>
       </c>
       <c r="I77" s="14" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J77" s="14" t="n">
-        <v>0.95</v>
+        <v>3.6</v>
       </c>
       <c r="K77" s="14" t="n">
-        <v>0.85</v>
+        <v>4.5</v>
       </c>
       <c r="L77" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="M77" s="5" t="s">
-        <v>53</v>
-      </c>
+      <c r="M77" s="5"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="11" t="n">
         <v>73</v>
       </c>
       <c r="B78" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C78" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="C78" s="11" t="s">
+      <c r="D78" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E78" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F78" s="12" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="I78" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J78" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K78" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L78" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="11"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D78" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E78" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F78" s="12" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="G78" s="12" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="H78" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I78" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K78" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L78" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" s="11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F79" s="14" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="G79" s="14" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="H79" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="I79" s="14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J79" s="14" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="K79" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L79" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="11" t="n">
-        <v>75</v>
-      </c>
-      <c r="B80" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="C80" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="D80" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E80" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F80" s="12" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="G80" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="H80" s="12" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="I80" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J80" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K80" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L80" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="11"/>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="5" t="n">
-        <v>76</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F81" s="14" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="G81" s="14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H81" s="14" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="I81" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J81" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="K81" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="L81" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" s="5"/>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="11" t="n">
-        <v>77</v>
-      </c>
-      <c r="B82" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="C82" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="D82" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E82" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L82" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="11"/>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="5" t="n">
-        <v>78</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F83" s="14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G83" s="14" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H83" s="14" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="I83" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J83" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="K83" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="L83" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="5"/>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="11" t="n">
-        <v>79</v>
-      </c>
-      <c r="B84" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="C84" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="D84" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E84" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F84" s="12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G84" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="H84" s="12" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="I84" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J84" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K84" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L84" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="11"/>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F85" s="14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G85" s="14" t="n">
-        <v>32</v>
-      </c>
-      <c r="H85" s="14" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="I85" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J85" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="K85" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="L85" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="5"/>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="11" t="n">
-        <v>81</v>
-      </c>
-      <c r="B86" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="D86" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E86" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F86" s="12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G86" s="12" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="H86" s="12" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="I86" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J86" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K86" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L86" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="11"/>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="5" t="n">
-        <v>82</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F87" s="14" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="G87" s="14" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="H87" s="14" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="I87" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J87" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K87" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="L87" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" s="5"/>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="11" t="n">
-        <v>83</v>
-      </c>
-      <c r="B88" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C88" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D88" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E88" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F88" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="G88" s="12" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="H88" s="12" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="I88" s="12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J88" s="12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K88" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L88" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" s="11"/>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="5" t="n">
-        <v>84</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F89" s="14" t="n">
-        <v>22</v>
-      </c>
-      <c r="G89" s="14" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="H89" s="14" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="I89" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J89" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K89" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="L89" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" s="5"/>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="11" t="n">
-        <v>85</v>
-      </c>
-      <c r="B90" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C90" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D90" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E90" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F90" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G90" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="H90" s="12" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="I90" s="12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J90" s="12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K90" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L90" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" s="11"/>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="5" t="n">
-        <v>86</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F91" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G91" s="14" t="n">
-        <v>33</v>
-      </c>
-      <c r="H91" s="14" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="I91" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J91" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K91" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="L91" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" s="5"/>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="11" t="n">
-        <v>87</v>
-      </c>
-      <c r="B92" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="C92" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="D92" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E92" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F92" s="12" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="G92" s="12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H92" s="12" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="I92" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J92" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K92" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L92" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" s="11"/>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="5" t="n">
-        <v>88</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F93" s="14" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="G93" s="14" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H93" s="14" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="I93" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J93" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="K93" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="L93" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" s="5"/>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="3" t="s">
-        <v>120</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:M93"/>
+  <autoFilter ref="A5:M78"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -6067,7 +5377,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -6080,7 +5390,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6090,7 +5400,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6098,37 +5408,37 @@
         <v>23</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="K5" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="L5" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6136,31 +5446,31 @@
         <v>1</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>-11</v>
+        <v>-13</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>28.5</v>
+        <v>1.5</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>1.7</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>20.3</v>
+        <v>18.5</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="K6" s="16" t="n">
         <v>242.2</v>
@@ -6174,31 +5484,31 @@
         <v>2</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C7" s="14" t="n">
-        <v>15.6</v>
+        <v>5</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>17.3</v>
+        <v>16</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>22.6</v>
+        <v>20.5</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="K7" s="17" t="n">
         <v>108.1</v>
@@ -6212,31 +5522,31 @@
         <v>3</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>82</v>
+        <v>129</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>16.6</v>
+        <v>18.3</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>24.6</v>
+        <v>16.3</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>1.5</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>28.4</v>
+        <v>18.8</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="K8" s="16" t="n">
         <v>242.2</v>
@@ -6250,31 +5560,31 @@
         <v>4</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="C9" s="14" t="n">
-        <v>15.6</v>
+        <v>18.2</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>7</v>
+        <v>29.6</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>19.8</v>
+        <v>14.2</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>11.6</v>
+        <v>23.8</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>6.3</v>
+        <v>1.5</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="K9" s="17" t="n">
         <v>108.1</v>
@@ -6288,37 +5598,37 @@
         <v>5</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>26.9</v>
+        <v>18.3</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>27.2</v>
+        <v>15.7</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>21.6</v>
+        <v>14.2</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>15</v>
+        <v>19.4</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>268</v>
+        <v>108.1</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>5.4</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6326,42 +5636,80 @@
         <v>6</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C11" s="14" t="n">
-        <v>-14</v>
+        <v>27.5</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>-10</v>
+        <v>29.5</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>26</v>
+        <v>1.6</v>
       </c>
       <c r="F11" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="K11" s="17" t="n">
+        <v>268</v>
+      </c>
+      <c r="L11" s="17" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>-12</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>-8</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F12" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="G11" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="H11" s="14" t="n">
+      <c r="G12" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H12" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="15" t="n">
+      <c r="I12" s="13" t="n">
         <v>35</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J12" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="K12" s="16" t="n">
+        <v>242.2</v>
+      </c>
+      <c r="L12" s="16" t="n">
+        <v>45.7</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="K11" s="17" t="n">
-        <v>242.2</v>
-      </c>
-      <c r="L11" s="17" t="n">
-        <v>45.7</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -6380,7 +5728,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -6395,7 +5743,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6405,7 +5753,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6413,25 +5761,25 @@
         <v>23</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="H5" s="10" t="s">
         <v>144</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6439,23 +5787,23 @@
         <v>1</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E6" s="18"/>
       <c r="F6" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6463,23 +5811,23 @@
         <v>2</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>157</v>
-      </c>
       <c r="D7" s="5" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E7" s="19"/>
       <c r="F7" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6487,23 +5835,23 @@
         <v>3</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E8" s="20"/>
       <c r="F8" s="11" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6511,23 +5859,23 @@
         <v>4</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E9" s="21"/>
       <c r="F9" s="5" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6535,23 +5883,23 @@
         <v>5</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E10" s="22"/>
       <c r="F10" s="11" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6559,23 +5907,23 @@
         <v>6</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="E11" s="23"/>
       <c r="F11" s="5" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6583,23 +5931,23 @@
         <v>7</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="E12" s="24"/>
       <c r="F12" s="11" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6607,23 +5955,23 @@
         <v>8</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="E13" s="25"/>
       <c r="F13" s="5" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6631,23 +5979,23 @@
         <v>9</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E14" s="26"/>
       <c r="F14" s="11" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6655,23 +6003,23 @@
         <v>10</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E15" s="27"/>
       <c r="F15" s="5" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6679,23 +6027,23 @@
         <v>11</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E16" s="28"/>
       <c r="F16" s="11" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6703,23 +6051,23 @@
         <v>12</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="E17" s="29"/>
       <c r="F17" s="5" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6727,23 +6075,23 @@
         <v>13</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="E18" s="30"/>
       <c r="F18" s="11" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6751,47 +6099,47 @@
         <v>14</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E19" s="31"/>
       <c r="F19" s="5" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="n">
         <v>15</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="E20" s="32"/>
       <c r="F20" s="11" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6799,23 +6147,23 @@
         <v>16</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="E21" s="33"/>
+        <v>208</v>
+      </c>
+      <c r="E21" s="28"/>
       <c r="F21" s="5" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6823,23 +6171,23 @@
         <v>17</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>151</v>
+        <v>210</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="E22" s="34"/>
+        <v>212</v>
+      </c>
+      <c r="E22" s="33"/>
       <c r="F22" s="11" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6847,23 +6195,23 @@
         <v>18</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="E23" s="35"/>
+        <v>216</v>
+      </c>
+      <c r="E23" s="34"/>
       <c r="F23" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6871,23 +6219,23 @@
         <v>19</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="E24" s="36"/>
+        <v>220</v>
+      </c>
+      <c r="E24" s="34"/>
       <c r="F24" s="11" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6895,23 +6243,23 @@
         <v>20</v>
       </c>
       <c r="B25" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>230</v>
-      </c>
       <c r="D25" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E25" s="36"/>
+        <v>222</v>
+      </c>
+      <c r="E25" s="35"/>
       <c r="F25" s="5" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6919,23 +6267,23 @@
         <v>21</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="E26" s="37"/>
+        <v>226</v>
+      </c>
+      <c r="E26" s="36"/>
       <c r="F26" s="11" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6943,23 +6291,23 @@
         <v>22</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="E27" s="38"/>
+        <v>230</v>
+      </c>
+      <c r="E27" s="37"/>
       <c r="F27" s="5" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6967,23 +6315,23 @@
         <v>23</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="E28" s="39"/>
+        <v>234</v>
+      </c>
+      <c r="E28" s="38"/>
       <c r="F28" s="11" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6991,23 +6339,23 @@
         <v>24</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="E29" s="40"/>
+        <v>238</v>
+      </c>
+      <c r="E29" s="39"/>
       <c r="F29" s="5" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7015,23 +6363,23 @@
         <v>25</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="E30" s="41"/>
+        <v>241</v>
+      </c>
+      <c r="E30" s="40"/>
       <c r="F30" s="11" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="G30" s="11" t="s">
         <v>243</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7039,23 +6387,23 @@
         <v>26</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="E31" s="42"/>
+        <v>212</v>
+      </c>
+      <c r="E31" s="41"/>
       <c r="F31" s="5" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7063,23 +6411,23 @@
         <v>27</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="E32" s="43"/>
+        <v>216</v>
+      </c>
+      <c r="E32" s="42"/>
       <c r="F32" s="11" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7087,23 +6435,23 @@
         <v>28</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="E33" s="44"/>
+        <v>220</v>
+      </c>
+      <c r="E33" s="43"/>
       <c r="F33" s="5" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7111,23 +6459,23 @@
         <v>29</v>
       </c>
       <c r="B34" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="E34" s="44"/>
+      <c r="F34" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="C34" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="E34" s="45"/>
-      <c r="F34" s="11" t="s">
-        <v>263</v>
-      </c>
       <c r="G34" s="11" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7135,23 +6483,23 @@
         <v>30</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="E35" s="46"/>
+        <v>226</v>
+      </c>
+      <c r="E35" s="45"/>
       <c r="F35" s="5" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7159,23 +6507,23 @@
         <v>31</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="E36" s="47"/>
+        <v>230</v>
+      </c>
+      <c r="E36" s="46"/>
       <c r="F36" s="11" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7183,23 +6531,23 @@
         <v>32</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="E37" s="48"/>
+        <v>234</v>
+      </c>
+      <c r="E37" s="47"/>
       <c r="F37" s="5" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7207,23 +6555,23 @@
         <v>33</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="E38" s="49"/>
+        <v>238</v>
+      </c>
+      <c r="E38" s="48"/>
       <c r="F38" s="11" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7231,23 +6579,23 @@
         <v>34</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="E39" s="50"/>
+        <v>241</v>
+      </c>
+      <c r="E39" s="49"/>
       <c r="F39" s="5" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7255,23 +6603,23 @@
         <v>35</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="E40" s="51"/>
+        <v>212</v>
+      </c>
+      <c r="E40" s="50"/>
       <c r="F40" s="11" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7279,23 +6627,23 @@
         <v>36</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>284</v>
+        <v>215</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="E41" s="52"/>
+        <v>216</v>
+      </c>
+      <c r="E41" s="51"/>
       <c r="F41" s="5" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7303,23 +6651,23 @@
         <v>37</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="E42" s="53"/>
+        <v>220</v>
+      </c>
+      <c r="E42" s="51"/>
       <c r="F42" s="11" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7327,23 +6675,23 @@
         <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E43" s="53"/>
+        <v>222</v>
+      </c>
+      <c r="E43" s="52"/>
       <c r="F43" s="5" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7351,23 +6699,23 @@
         <v>39</v>
       </c>
       <c r="B44" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="E44" s="53"/>
+      <c r="F44" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="C44" s="11" t="s">
-        <v>290</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="E44" s="54"/>
-      <c r="F44" s="11" t="s">
-        <v>291</v>
-      </c>
       <c r="G44" s="11" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7375,23 +6723,23 @@
         <v>40</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="E45" s="55"/>
+        <v>230</v>
+      </c>
+      <c r="E45" s="54"/>
       <c r="F45" s="5" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7399,23 +6747,23 @@
         <v>41</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="E46" s="56"/>
+        <v>234</v>
+      </c>
+      <c r="E46" s="55"/>
       <c r="F46" s="11" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7423,23 +6771,23 @@
         <v>42</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="E47" s="57"/>
+        <v>238</v>
+      </c>
+      <c r="E47" s="56"/>
       <c r="F47" s="5" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7447,56 +6795,32 @@
         <v>43</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="E48" s="58"/>
+        <v>241</v>
+      </c>
+      <c r="E48" s="57"/>
       <c r="F48" s="11" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="E49" s="59"/>
-      <c r="F49" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="H49" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="s">
-        <v>308</v>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>297</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:H49"/>
+  <autoFilter ref="A5:H48"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/output/twinmotion/VJH-TM-001_Twinmotion_lists.xlsx
+++ b/output/twinmotion/VJH-TM-001_Twinmotion_lists.xlsx
@@ -5299,7 +5299,7 @@
         <v>17.55</v>
       </c>
       <c r="H77" s="14" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="I77" s="14" t="n">
         <v>3.6</v>
